--- a/monte_carlo_results.xlsx
+++ b/monte_carlo_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crvia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0983277D-5273-4EB2-A33F-451AA1A4C7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8CA466-5080-4FD6-906A-0E2C2C9D95B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,9 +23,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
-    <t>Monte Carlo Robustness Analysis</t>
-  </si>
-  <si>
     <t>SEED = 42 | 100,000 replications per weighting regime | Generated from monte_carlo.py</t>
   </si>
   <si>
@@ -93,6 +90,9 @@
   </si>
   <si>
     <t>monte_carlo_results.xlsx</t>
+  </si>
+  <si>
+    <t>Monte Carlo Sensitivity Analysis</t>
   </si>
 </sst>
 </file>
@@ -414,7 +414,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20.85" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -425,7 +425,7 @@
     </row>
     <row r="2" spans="1:7" ht="22.35" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -436,30 +436,30 @@
     </row>
     <row r="3" spans="1:7" ht="22.35" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2">
         <v>1</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -505,7 +505,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2">
         <v>1</v>
@@ -528,7 +528,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2">
         <v>1</v>
@@ -551,7 +551,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="2">
         <v>1</v>
@@ -592,21 +592,21 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16.8">
       <c r="A1" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>42</v>
@@ -614,7 +614,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5">
         <v>100000</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -630,18 +630,18 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
         <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
         <v>22</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
